--- a/02_DIA_inicio_2026_analisis_assets/rbd_9699_colegio-naciones-unidas_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9699_colegio-naciones-unidas_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7D502BC-57E6-406C-9BBD-99E8E0FEA6E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6937BF46-B877-4FAF-B639-7DBE5744AF0C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C79DCB2A-2759-4547-87CC-1DDAB1BFCC78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56C8F8D4-CD02-4EA3-AB1F-3C0F28E2EBF3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6BC9969-80D4-41A4-ABEC-A28A04A2EE53}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7BB8074-DA77-4593-8B03-5B76327DA29F}"/>
 </file>